--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -477,10 +477,20 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Fuentes (original)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Links fuentes (original)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Clasificación preexistencia BO</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Justificación preexistencia BO</t>
         </is>
@@ -489,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,14 +507,19 @@
           <t>Ángeles Argentina</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Desarrollo de una explotación de litio en el Salar de Diablillos, departamento Los Andes, Salta, con infraestructura de extracción de salmuera y una planta de producción comercial. La iniciativa prevé una expansión por etapas de la capacidad productiva.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Xizang Zhufeng Resources Co Ltd (Tibet Summit) (China)</t>
+          <t>Tibet Summit Resources / Xizang Zhufeng Resources Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Potasio y Litio de Argentina SA</t>
+          <t>Potasio y Litio de Argentina S.A. (PLASA)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -540,14 +555,24 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841]; Casa Rosada [https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Globaris; Gobierno de Salta; Casa Rosada; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841; https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,6 +580,11 @@
           <t>Arenas de Cercanía</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Proyecto para extraer y procesar arena silícea de cercanía en Río Negro como agente sostén para operaciones de fractura hidráulica en Vaca Muerta. La iniciativa se orienta al abastecimiento regional y a reducir distancias logísticas respecto de otras cuencas de suministro.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Minera del Mojotoro (Argentina); Minera Orosmayo (Argentina)</t>
@@ -577,7 +607,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rio Negro</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,14 +628,24 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; Gobierno de Río Negro [https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Globaris; Infobae; Gobierno de Río Negro; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/; https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -613,24 +653,29 @@
           <t>Bajo del Choique–La Invernada</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Desarrollo no convencional de petróleo y gas en los bloques Bajo del Choique–La Invernada, en Vaca Muerta. Contempla la perforación de más de 600 pozos, plantas de procesamiento, ductos e infraestructura asociada, con objetivos de hasta 100.000 barriles diarios de petróleo y 12 millones de m³ diarios de gas.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A (Argentina)</t>
+          <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pluspetrol Cuenca Neuquina S.R.L</t>
+          <t>Pluspetrol Cuenca Neuquina S.R.L.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -656,14 +701,24 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Neuquén [https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp]; EconoJournal [https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2047621135127269495]; Clarín [https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html]</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -671,6 +726,11 @@
           <t>Duplicar Norte</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Construcción de un oleoducto de aproximadamente 207 km entre el área de Auca Mahuida/Puesto Hernández, en Neuquén, y Allen, en Río Negro, junto con obras de repotenciación y medición. La ampliación busca sumar capacidad de transporte de crudo desde Vaca Muerta.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Oldelval (Argentina)</t>
@@ -683,17 +743,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -714,19 +774,34 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Oldelval (12/03/2026) [https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/]; Oldelval (04/07/2025) [https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Globaris; Oldelval; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/; https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>El Pachón</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Desarrollo de una mina de cobre y molibdeno de gran escala en San Juan, con plata como subproducto e infraestructura de procesamiento asociada. La solicitud al RIGI corresponde a la primera fase del proyecto y está orientada a producción para exportación.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -772,14 +847,24 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -787,6 +872,11 @@
           <t>El Trapial</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Desarrollo de petróleo no convencional en el área El Trapial Este, en la formación Vaca Muerta, provincia de Neuquén. El programa prevé perforación, completación e infraestructura de superficie para ampliar la producción del bloque.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Chevron (Estados Unidos)</t>
@@ -794,12 +884,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -825,111 +915,138 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Chevron [https://www.chevron.com/worldwide/argentina]; Infobae [https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/]; Clarín [https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html]</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Globaris; Chevron; Infobae; Clarín; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>https://www.chevron.com/worldwide/argentina; https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/; https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fértil Pampa</t>
+          <t>NCA+ (Nuevo Central Argentino)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Programa de inversión ferroviaria de carga de Nuevo Central Argentino para mejorar infraestructura y capacidad operativa de la red que vincula centros productivos con puertos de exportación. El proyecto alcanza tramos en Buenos Aires, Santa Fe, Santiago del Estero y Chaco.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>Nuevo Central Argentino S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>Nuevo Central Argentino S.A.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Ferroviario</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Buenos Aires; Santa Fe; Santiago del Estero; Chaco</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="L8">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="P8" s="2">
-        <v>46136</v>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Ministerio de Economía / Boletín Oficial [https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto]; Nuevo Central Argentino [https://www.nca.com.ar/Nuestra-red]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Globaris; Ministerio de Economía / Boletín Oficial; Nuevo Central Argentino; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto; https://www.nca.com.ar/Nuestra-red; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>Parque Eólico La Rinconada</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Construcción de un parque eólico de 94,5 MW en Olavarría, provincia de Buenos Aires, integrado por 21 aerogeneradores. La energía se destinará principalmente a abastecer la planta siderúrgica de Siderca en Campana.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CNGR (China)</t>
+          <t>Tenaris (Argentina)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material</t>
+          <t>Vientos La Rinconada S.A.U.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Eólico</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="L9">
-        <v>1151</v>
+        <v>206</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -937,38 +1054,58 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <v>46111</v>
+        <v>45805</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Tenaris [https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Globaris; Tenaris; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LL Oil</t>
+          <t>Planta de Tratamiento Los Toldos</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Desarrollo del área no convencional Los Toldos II Este, en Neuquén, con una planta central de procesamiento de crudo, perforación de pozos y sistemas de recolección y evacuación. El proyecto apunta a alcanzar una producción cercana a 70.000 barriles diarios.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,7 +1119,7 @@
         </is>
       </c>
       <c r="L10">
-        <v>25000</v>
+        <v>6391</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -990,52 +1127,72 @@
         </is>
       </c>
       <c r="P10" s="2">
-        <v>46157</v>
+        <v>46118</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Techint Ingeniería y Construcción [https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este]; Vaca Muerta News [https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Globaris; Techint Ingeniería y Construcción; Vaca Muerta News; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este; https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
+          <t>Pozuelos Pastos Grandes (PPG)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A (Argentina)</t>
+          <t>Ganfeng Lithium (China); Lithium Argentina AG (Suiza)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lithea Inc.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L11">
-        <v>1000</v>
+        <v>4245</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1043,57 +1200,72 @@
         </is>
       </c>
       <c r="P11" s="2">
-        <v>46157</v>
+        <v>46081</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827]; Lithium Argentina [https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Globaris; Gobierno de Salta; Lithium Argentina; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827; https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sal de Vida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Desarrollo de litio en el Salar del Hombre Muerto, Catamarca, con extracción de salmuera e instalaciones de procesamiento. La primera etapa prevé una capacidad de aproximadamente 15.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Petrobras (Brazil); Dow (Argentina)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sal de Vida S.A.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L12">
-        <v>360</v>
+        <v>818</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1101,57 +1273,67 @@
         </is>
       </c>
       <c r="P12" s="2">
-        <v>46099</v>
+        <v>45758</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Rio Tinto [https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project]; Infobae (07/10/2025) [https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/]; Infobae (13/05/2026) [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Globaris; Rio Tinto; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project; https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Desarrollo integrado de petróleo no convencional en los bloques Loma Jarillosa Este y Puesto Silva Oeste, en Vaca Muerta, mediante perforación en modo factoría, una planta central de procesamiento y sistemas compartidos de evacuación. El plan busca elevar la producción conjunta hasta unos 20.000 barriles equivalentes diarios en tres años.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Minera Agua Rica LLC Sucursal Argentina</t>
+          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="L13">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1159,112 +1341,145 @@
         </is>
       </c>
       <c r="P13" s="2">
-        <v>45887</v>
+        <v>46157</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; GeoPark [https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/]; EconoJournal [https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/]</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Globaris; GeoPark; EconoJournal; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NCA+ (Nuevo Central Argentino)</t>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ampliación de la capacidad de procesamiento, fraccionamiento y transporte de líquidos del gas natural provenientes de la Cuenca Neuquina. Las obras abarcan instalaciones en Neuquén y el corredor de transporte hasta el complejo de fraccionamiento y exportación de Bahía Blanca, con un aumento proyectado de 1.500 toneladas diarias.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nuevo Central Argentino (Argentina)</t>
+          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nuevo Central Argentino</t>
+          <t>Compañía Mega S.A. – Sucursal Dedicada</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ferroviario</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Múltiples (Buenos Aires, Santa Fe, Santiago del Estero, Chaco)</t>
+          <t>Neuquén; Río Negro; La Pampa; Buenos Aires</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="L14">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="P14" s="2">
+        <v>46099</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/]; Compañía MEGA [https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2083255389399744911]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Globaris; EconoJournal; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/; https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/; https://x.com/LuisCaputoAR/status/2083255389399744911</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Parque Eólico La Rinconada</t>
+          <t>Minera Agua Rica (MARA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenaris (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vientos La Rinconada S.A.U.</t>
+          <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Eólico</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L15">
-        <v>206</v>
+        <v>4000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1272,57 +1487,72 @@
         </is>
       </c>
       <c r="P15" s="2">
-        <v>45805</v>
+        <v>45887</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Planta de Tratamiento Los Toldos</t>
+          <t>Fértil Pampa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Petroquímica / Fertilizantes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="L16">
-        <v>6391</v>
+        <v>2400</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1330,33 +1560,48 @@
         </is>
       </c>
       <c r="P16" s="2">
-        <v>46118</v>
+        <v>46136</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Pampa Energía [https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/]; International Finance Corporation [https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p]; El Cronista [https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/]; La Nación [https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2083255389399744911]</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pozuelos Pastos Grandes (PPG)</t>
+          <t>Jama Solaroz</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ganfeng (China); Lithium Argentina (Suiza)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lithea Inc.</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1616,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1380,7 +1625,7 @@
         </is>
       </c>
       <c r="L17">
-        <v>4245</v>
+        <v>1151</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1388,57 +1633,67 @@
         </is>
       </c>
       <c r="P17" s="2">
-        <v>46081</v>
+        <v>46111</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Jujuy [https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116]; El Tribuno de Jujuy [https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sal de Vida</t>
+          <t>LLL Oil</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sal de Vida S.A.</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="L18">
-        <v>818</v>
+        <v>25000</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1446,11 +1701,89 @@
         </is>
       </c>
       <c r="P18" s="2">
-        <v>45758</v>
+        <v>46157</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF [https://www.instagram.com/p/DYX1JXjj-bC/]; EconoJournal [https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/]; Reuters [https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/]</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bandurria Norte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vista Energy (Argentina)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Neuquén</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="L19">
+        <v>5800</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P19" s="2">
+        <v>46224</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/]; Vista Energy / SEC [https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm]; Oil &amp; Gas Journal [https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development]</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841]; Casa Rosada [https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841]; o de Salta [https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta]; Casa Rosada [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; Gobierno de Río Negro [https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; I [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; fobae [https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta]; Gobier; o de Río Negro; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Neuquén [https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp]; EconoJournal [https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2047621135127269495]; Clarín [https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp]; o de Neuqué [https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/]; Eco [https://x.com/LuisCaputoAR/status/2047621135127269495]; oJour [https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html]; al; Luis Caputo; Clarí; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Oldelval (12/03/2026) [https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/]; Oldelval (04/07/2025) [https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Oldelval [https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/]; I [https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/]; fobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gle [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; core [https://x.com/LuisCaputoAR/status/1957458679835594969]; Luis Caputo [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Reuters [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -882,6 +882,11 @@
           <t>Chevron (Estados Unidos)</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Petróleo y Gas</t>
@@ -915,7 +920,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Chevron [https://www.chevron.com/worldwide/argentina]; Infobae [https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/]; Clarín [https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Chevro [https://www.chevron.com/worldwide/argentina]; I [https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/]; fobae [https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html]; Clarí; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -985,7 +990,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Ministerio de Economía / Boletín Oficial [https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto]; Nuevo Central Argentino [https://www.nca.com.ar/Nuestra-red]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Mi [https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto]; isterio de Eco [https://www.nca.com.ar/Nuestra-red]; omía / Boletí [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; Oficial; Nuevo Ce; tral Arge; ti; o; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1058,7 +1063,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Tenaris [https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Te [https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina]; aris [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1131,7 +1136,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Techint Ingeniería y Construcción [https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este]; Vaca Muerta News [https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Techi [https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este]; t I [https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm]; ge [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; iería y Co; strucció; Vaca Muerta News; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1204,7 +1209,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827]; Lithium Argentina [https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827]; o de Salta [https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025]; Lithium Arge [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; ti; a; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1277,7 +1282,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Rio Tinto [https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project]; Infobae (07/10/2025) [https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/]; Infobae (13/05/2026) [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Rio Ti [https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project]; to [https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/]; I [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1312,6 +1317,11 @@
           <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GeoPark</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Petróleo y Gas</t>
@@ -1345,7 +1355,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; GeoPark [https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/]; EconoJournal [https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; GeoPark [https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/]; Eco [https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/]; oJour; al; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1418,7 +1428,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/]; Compañía MEGA [https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2083255389399744911]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Eco [https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/]; oJour [https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/]; al [https://x.com/LuisCaputoAR/status/2083255389399744911]; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1491,7 +1501,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gle [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; core [https://x.com/LuisCaputoAR/status/1957458679835594969]; Luis Caputo [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Reuters [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1564,7 +1574,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Pampa Energía [https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/]; International Finance Corporation [https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p]; El Cronista [https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/]; La Nación [https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2083255389399744911]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Pampa E [https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/]; ergía [https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p]; I [https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/]; ter [https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/]; atio; al Fi; a; ce Corporatio; El Cro; ista; La Nació; Luis Caputo; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1637,7 +1647,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Jujuy [https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116]; El Tribuno de Jujuy [https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116]; o de Jujuy [https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi]; El Tribu [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; o de Jujuy; I; fobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1672,6 +1682,11 @@
           <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Petróleo y Gas</t>
@@ -1705,7 +1720,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF [https://www.instagram.com/p/DYX1JXjj-bC/]; EconoJournal [https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/]; Reuters [https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF [https://www.instagram.com/p/DYX1JXjj-bC/]; Eco [https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/]; oJour [https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/]; al; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -1740,6 +1755,11 @@
           <t>Vista Energy (Argentina)</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vista Energy</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Petróleo y Gas</t>
@@ -1773,7 +1793,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/]; Vista Energy / SEC [https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm]; Oil &amp; Gas Journal [https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development]</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Eco [https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/]; oJour [https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm]; al [https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development]; Vista E; ergy / SEC; Oil &amp; Gas Jour; al; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841]; o de Salta [https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta]; Casa Rosada [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/vinculos-con-empresa-minera-china-para-el-ingreso-de-productos-saltenios-al-pais-asiatico-104841]; Casa Rosada [https://www.casarosada.gob.ar/slider-principal/50224-el-presidente-se-reunio-con-autoridades-de-una-empresa-china-que-desarrolla-proyectos-de-extraccion-de-litio-en-salta]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; I [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; fobae [https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta]; Gobier; o de Río Negro; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; Gobierno de Río Negro [https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp]; o de Neuqué [https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/]; Eco [https://x.com/LuisCaputoAR/status/2047621135127269495]; oJour [https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html]; al; Luis Caputo; Clarí; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Neuquén [https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp]; EconoJournal [https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2047621135127269495]; Clarín [https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Oldelval [https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/]; I [https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/]; fobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Oldelval [https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/]; Oldelval [https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gle [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; core [https://x.com/LuisCaputoAR/status/1957458679835594969]; Luis Caputo [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Reuters [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Chevro [https://www.chevron.com/worldwide/argentina]; I [https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/]; fobae [https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html]; Clarí; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Chevron [https://www.chevron.com/worldwide/argentina]; Infobae [https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/]; Clarín [https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Mi [https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto]; isterio de Eco [https://www.nca.com.ar/Nuestra-red]; omía / Boletí [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; Oficial; Nuevo Ce; tral Arge; ti; o; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Ministerio de Economía / Boletín Oficial [https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto]; Nuevo Central Argentino [https://www.nca.com.ar/Nuestra-red]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Te [https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina]; aris [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Tenaris [https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Techi [https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este]; t I [https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm]; ge [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; iería y Co; strucció; Vaca Muerta News; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Techint Ingeniería y Construcción [https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este]; Vaca Muerta News [https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827]; o de Salta [https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025]; Lithium Arge [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; ti; a; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Salta [https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827]; Lithium Argentina [https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Rio Ti [https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project]; to [https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/]; I [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Rio Tinto [https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project]; Infobae [https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; GeoPark [https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/]; Eco [https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/]; oJour; al; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; GeoPark [https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/]; EconoJournal [https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Eco [https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/]; oJour [https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/]; al [https://x.com/LuisCaputoAR/status/2083255389399744911]; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/]; Compañía MEGA [https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/]; Luis Caputo [https://x.com/LuisCaputoAR/status/2083255389399744911]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gle [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; core [https://x.com/LuisCaputoAR/status/1957458679835594969]; Luis Caputo [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Reuters [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Glencore [https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects]; Luis Caputo [https://x.com/LuisCaputoAR/status/1957458679835594969]; Reuters [https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Pampa E [https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/]; ergía [https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p]; I [https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/]; ter [https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/]; atio; al Fi; a; ce Corporatio; El Cro; ista; La Nació; Luis Caputo; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Pampa Energía [https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/]; International Finance Corporation [https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p]; El Cronista [https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/]; La Nación [https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/]; Luis Caputo</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobier [https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116]; o de Jujuy [https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi]; El Tribu [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]; o de Jujuy; I; fobae; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Gobierno de Jujuy [https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116]; El Tribuno de Jujuy [https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi]; Infobae [https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF [https://www.instagram.com/p/DYX1JXjj-bC/]; Eco [https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/]; oJour [https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/]; al; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF [https://www.instagram.com/p/DYX1JXjj-bC/]; EconoJournal [https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/]; Reuters [https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Eco [https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/]; oJour [https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm]; al [https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development]; Vista E; ergy / SEC; Oil &amp; Gas Jour; al; auditoría 2026-08-08</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; EconoJournal [https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/]; Vista Energy / SEC [https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm]; Oil &amp; Gas Journal [https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development]</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -485,16 +485,6 @@
           <t>Links fuentes (original)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Clasificación preexistencia BO</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Justificación preexistencia BO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -1797,6 +1797,79 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Argentina LNG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Neuquén; Río Negro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="L20">
+        <v>51000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P20" s="2">
+        <v>46247</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; YPF / Argentina LNG [https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf]; La Nación [https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/]; Infobae [https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/]; Data Energía [https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370]</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -1830,7 +1830,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
